--- a/CPRD Raw Analysis/Results/Output_overall_healthcare_roles-Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_overall_healthcare_roles-Raw.xlsx
@@ -375,27 +375,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B2">
-        <v>413255</v>
+        <v>404780</v>
       </c>
       <c r="C2">
-        <v>38.14</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B3">
-        <v>473745</v>
+        <v>427552</v>
       </c>
       <c r="C3">
-        <v>43.73</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="4">
@@ -405,10 +405,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>101524</v>
+        <v>40711</v>
       </c>
       <c r="C4">
-        <v>9.369999999999999</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="5">
@@ -418,10 +418,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>94918</v>
+        <v>42958</v>
       </c>
       <c r="C5">
-        <v>8.76</v>
+        <v>4.69</v>
       </c>
     </row>
   </sheetData>
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -459,1063 +459,595 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Associate Practitioner - General Practitioner</t>
         </is>
       </c>
       <c r="C2">
-        <v>79</v>
+        <v>2122</v>
       </c>
       <c r="D2">
-        <v>0.007291576291116646</v>
+        <v>0.2316591357433016</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clerical Worker</t>
+          <t>Community Practitioner</t>
         </is>
       </c>
       <c r="C3">
-        <v>52837</v>
+        <v>43287</v>
       </c>
       <c r="D3">
-        <v>4.876772360680129</v>
+        <v>4.725649862827661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clinical Coder</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="C4">
-        <v>4416</v>
+        <v>11921</v>
       </c>
       <c r="D4">
-        <v>0.407589884830014</v>
+        <v>1.301417793212016</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Community Administrator</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="C5">
-        <v>25691</v>
+        <v>303981</v>
       </c>
       <c r="D5">
-        <v>2.371239069557946</v>
+        <v>33.18566246106718</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Desktop Support Administrator</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="C6">
-        <v>24519</v>
+        <v>4765</v>
       </c>
       <c r="D6">
-        <v>2.263065304834038</v>
+        <v>0.520195938650722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Desktop Support Technician</t>
+          <t>Salaried General Practitioner</t>
         </is>
       </c>
       <c r="C7">
-        <v>1098</v>
+        <v>26363</v>
       </c>
       <c r="D7">
-        <v>0.1013436806031149</v>
+        <v>2.87805362657901</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dispenser</t>
+          <t>Sessional GP</t>
         </is>
       </c>
       <c r="C8">
-        <v>5766</v>
+        <v>12341</v>
       </c>
       <c r="D8">
-        <v>0.5321927708174503</v>
+        <v>1.347269271540096</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Health Records Administrator</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="C9">
-        <v>541</v>
+        <v>427552</v>
       </c>
       <c r="D9">
-        <v>0.04993345282903931</v>
+        <v>46.67593157649391</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Helpdesk Administrator</t>
+          <t>Associate Practitioner - Nurse</t>
         </is>
       </c>
       <c r="C10">
-        <v>1225</v>
+        <v>1950</v>
       </c>
       <c r="D10">
-        <v>0.1130655817293404</v>
+        <v>0.2128818636660877</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Community Mental Health Nurse</t>
         </is>
       </c>
       <c r="C11">
-        <v>85436</v>
+        <v>90</v>
       </c>
       <c r="D11">
-        <v>7.88560901275749</v>
+        <v>0.009825316784588662</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Medical Records Clerk</t>
+          <t>Community Nurse</t>
         </is>
       </c>
       <c r="C12">
-        <v>1011</v>
+        <v>15343</v>
       </c>
       <c r="D12">
-        <v>0.0933137168394801</v>
+        <v>1.674998171399376</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Medical Secretary</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="C13">
-        <v>15820</v>
+        <v>212</v>
       </c>
       <c r="D13">
-        <v>1.460161226904624</v>
+        <v>0.02314407953703107</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Medical Student</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="C14">
-        <v>236</v>
+        <v>1580</v>
       </c>
       <c r="D14">
-        <v>0.02178243043928517</v>
+        <v>0.1724888946627788</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Receptionist</t>
+          <t>Sister/Charge Nurse</t>
         </is>
       </c>
       <c r="C15">
-        <v>101721</v>
+        <v>2480</v>
       </c>
       <c r="D15">
-        <v>9.388689011502231</v>
+        <v>0.2707420625086654</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Secretary</t>
+          <t>Specialist Nurse Practitioner</t>
         </is>
       </c>
       <c r="C16">
-        <v>13516</v>
+        <v>11985</v>
       </c>
       <c r="D16">
-        <v>1.2475056348194</v>
+        <v>1.308404685147724</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Senior Administrator</t>
+          <t>Staff Nurse</t>
         </is>
       </c>
       <c r="C17">
-        <v>18603</v>
+        <v>7071</v>
       </c>
       <c r="D17">
-        <v>1.717027768906873</v>
+        <v>0.7719423887091826</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>Advanced Practitioner</t>
         </is>
       </c>
       <c r="C18">
-        <v>3954</v>
+        <v>267</v>
       </c>
       <c r="D18">
-        <v>0.3649480082920913</v>
+        <v>0.0291484397942797</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Associate Specialist</t>
         </is>
       </c>
       <c r="C19">
-        <v>55535</v>
+        <v>192</v>
       </c>
       <c r="D19">
-        <v>5.125793535786872</v>
+        <v>0.02096067580712248</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>System Worker</t>
+          <t>Chiropodist/Podiatrist</t>
         </is>
       </c>
       <c r="C20">
-        <v>1251</v>
+        <v>111</v>
       </c>
       <c r="D20">
-        <v>0.1154653410150243</v>
+        <v>0.01211789070099268</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate Practitioner - General Practitioner</t>
+          <t>Clinical Psychologist</t>
         </is>
       </c>
       <c r="C21">
-        <v>2996</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>0.2765261084580439</v>
+        <v>0.0008733614919634368</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="C22">
-        <v>14349</v>
+        <v>2046</v>
       </c>
       <c r="D22">
-        <v>1.324390230395351</v>
+        <v>0.2233622015696489</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Counsellor</t>
         </is>
       </c>
       <c r="C23">
-        <v>401172</v>
+        <v>128</v>
       </c>
       <c r="D23">
-        <v>37.02754739063097</v>
+        <v>0.01397378387141499</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>Dietitian</t>
         </is>
       </c>
       <c r="C24">
-        <v>6025</v>
+        <v>79</v>
       </c>
       <c r="D24">
-        <v>0.5560980652402251</v>
+        <v>0.008624444733138937</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Salaried General Practitioner</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="C25">
-        <v>33882</v>
+        <v>37858</v>
       </c>
       <c r="D25">
-        <v>3.127255542982458</v>
+        <v>4.132964920343973</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sessional GP</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="C26">
-        <v>15321</v>
+        <v>837</v>
       </c>
       <c r="D26">
-        <v>1.414104308306305</v>
+        <v>0.09137544609667457</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate Practitioner - Nurse</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="C27">
-        <v>2457</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>0.2267772524971342</v>
+        <v>0.0003275105594862888</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Community Mental Health Nurse</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="C28">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="D28">
-        <v>0.008583754368023392</v>
+        <v>0.03646284228947348</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Community Nurse</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="C29">
-        <v>18702</v>
+        <v>211</v>
       </c>
       <c r="D29">
-        <v>1.726165313879285</v>
+        <v>0.02303490935053564</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Community Practitioner</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="C30">
-        <v>49421</v>
+        <v>217</v>
       </c>
       <c r="D30">
-        <v>4.561480909914883</v>
+        <v>0.02368993046950822</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Modern Matron</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="C31">
-        <v>224</v>
+        <v>474</v>
       </c>
       <c r="D31">
-        <v>0.02067484923050796</v>
+        <v>0.05174666839883363</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nurse Consultant</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="C32">
-        <v>1916</v>
+        <v>7</v>
       </c>
       <c r="D32">
-        <v>0.1768437996680948</v>
+        <v>0.000764191305468007</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nurse Manager</t>
+          <t>Specialist Practitioner</t>
         </is>
       </c>
       <c r="C33">
-        <v>2695</v>
+        <v>135</v>
       </c>
       <c r="D33">
-        <v>0.2487442798045489</v>
+        <v>0.01473797517688299</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sister/Charge Nurse</t>
+          <t>Therapist</t>
         </is>
       </c>
       <c r="C34">
-        <v>2965</v>
+        <v>51</v>
       </c>
       <c r="D34">
-        <v>0.2736648570020361</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Nurse</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Specialist Nurse Practitioner</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>14765</v>
-      </c>
-      <c r="D35">
-        <v>1.362786378966294</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Nurse</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Staff Nurse</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>8286</v>
-      </c>
-      <c r="D36">
-        <v>0.7647848246606648</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Advanced Practitioner</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>346</v>
-      </c>
-      <c r="D37">
-        <v>0.03193525818640961</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Assistant Practitioner</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>581</v>
-      </c>
-      <c r="D38">
-        <v>0.05362539019163001</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Associate Specialist</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>204</v>
-      </c>
-      <c r="D39">
-        <v>0.0188288805492126</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Chiropodist/Podiatrist</t>
-        </is>
-      </c>
-      <c r="C40">
-        <v>119</v>
-      </c>
-      <c r="D40">
-        <v>0.01098351365370735</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Clinical Assistant</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>580</v>
-      </c>
-      <c r="D41">
-        <v>0.05353309175756524</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Clinical Psychologist</t>
-        </is>
-      </c>
-      <c r="C42">
-        <v>8</v>
-      </c>
-      <c r="D42">
-        <v>0.0007383874725181412</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Consultant</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>2232</v>
-      </c>
-      <c r="D43">
-        <v>0.2060101048325614</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Counsellor</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>152</v>
-      </c>
-      <c r="D44">
-        <v>0.01402936197784468</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Dietitian</t>
-        </is>
-      </c>
-      <c r="C45">
-        <v>81</v>
-      </c>
-      <c r="D45">
-        <v>0.00747617315924618</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Health Care Support Worker</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>46310</v>
-      </c>
-      <c r="D46">
-        <v>4.27434048153939</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Healthcare Assistant</t>
-        </is>
-      </c>
-      <c r="C47">
-        <v>29189</v>
-      </c>
-      <c r="D47">
-        <v>2.694098991916503</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Medical Technical Officer - Pharmacy</t>
-        </is>
-      </c>
-      <c r="C48">
-        <v>873</v>
-      </c>
-      <c r="D48">
-        <v>0.08057653293854217</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Midwife</t>
-        </is>
-      </c>
-      <c r="C49">
-        <v>3</v>
-      </c>
-      <c r="D49">
-        <v>0.0002768953021943029</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Other Community Health Service</t>
-        </is>
-      </c>
-      <c r="C50">
-        <v>357</v>
-      </c>
-      <c r="D50">
-        <v>0.03295054096112206</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Paramedic</t>
-        </is>
-      </c>
-      <c r="C51">
-        <v>255</v>
-      </c>
-      <c r="D51">
-        <v>0.02353610068651575</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Paramedic Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="C52">
-        <v>271</v>
-      </c>
-      <c r="D52">
-        <v>0.02501287563155204</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Pharmacist</t>
-        </is>
-      </c>
-      <c r="C53">
-        <v>6001</v>
-      </c>
-      <c r="D53">
-        <v>0.5538829028226707</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Phlebotomist</t>
-        </is>
-      </c>
-      <c r="C54">
-        <v>6611</v>
-      </c>
-      <c r="D54">
-        <v>0.610184947602179</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Physician Assistant</t>
-        </is>
-      </c>
-      <c r="C55">
-        <v>22</v>
-      </c>
-      <c r="D55">
-        <v>0.002030565549424889</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Physiotherapist</t>
-        </is>
-      </c>
-      <c r="C56">
-        <v>493</v>
-      </c>
-      <c r="D56">
-        <v>0.04550312799393046</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Radiographer</t>
-        </is>
-      </c>
-      <c r="C57">
-        <v>30</v>
-      </c>
-      <c r="D57">
-        <v>0.00276895302194303</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Social Worker</t>
-        </is>
-      </c>
-      <c r="C58">
-        <v>9</v>
-      </c>
-      <c r="D58">
-        <v>0.000830685906582909</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="C59">
-        <v>140</v>
-      </c>
-      <c r="D59">
-        <v>0.01292178076906747</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Therapist</t>
-        </is>
-      </c>
-      <c r="C60">
-        <v>51</v>
-      </c>
-      <c r="D60">
-        <v>0.00470722013730315</v>
+        <v>0.005567679511266909</v>
       </c>
     </row>
   </sheetData>
